--- a/GWD Data/PVC Fittings PRICE.xlsx
+++ b/GWD Data/PVC Fittings PRICE.xlsx
@@ -1114,7 +1114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869AA113-8A05-4B22-8C8B-242FFB8FB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32509CE5-3297-4195-A0F5-398D934AB9A6}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/PVC Fittings PRICE.xlsx
+++ b/GWD Data/PVC Fittings PRICE.xlsx
@@ -1114,7 +1114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32509CE5-3297-4195-A0F5-398D934AB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84323A27-C2FA-4317-98ED-047923A9B9A6}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
